--- a/outputs/Erratic/Erratic - Low N_d_report.xlsx
+++ b/outputs/Erratic/Erratic - Low N_d_report.xlsx
@@ -511,13 +511,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.255789430178391</v>
+        <v>2.618881256095634</v>
       </c>
       <c r="E4" t="n">
-        <v>3.741670922677684</v>
+        <v>3.752493651897519</v>
       </c>
       <c r="F4" t="n">
-        <v>8.881784197001252e-16</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="5">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9148936562222048</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.22352087053255</v>
+        <v>2.438785168810843</v>
       </c>
       <c r="E5" t="n">
-        <v>3.687410933254335</v>
+        <v>3.616086550467038</v>
       </c>
       <c r="F5" t="n">
-        <v>4.314456814221444</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="6">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6512477582961196</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6188931838175</v>
+        <v>2.75401656194981</v>
       </c>
       <c r="E6" t="n">
-        <v>3.63863339311986</v>
+        <v>3.631337175662996</v>
       </c>
       <c r="F6" t="n">
-        <v>-30.34227088316621</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.052620417235779</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.046971129608794</v>
+        <v>2.347757294246383</v>
       </c>
       <c r="E7" t="n">
-        <v>3.649166618424402</v>
+        <v>3.585381007770356</v>
       </c>
       <c r="F7" t="n">
-        <v>7.962984195310066</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="8">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9473583755122015</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.009438428446471</v>
+        <v>2.327315946975768</v>
       </c>
       <c r="E8" t="n">
-        <v>3.655471372773817</v>
+        <v>3.584859263329847</v>
       </c>
       <c r="F8" t="n">
-        <v>11.46668577577905</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.07890882288633989</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.263776503827607</v>
+        <v>2.397516112297884</v>
       </c>
       <c r="E9" t="n">
-        <v>3.663661212113867</v>
+        <v>3.58665705445309</v>
       </c>
       <c r="F9" t="n">
-        <v>6.277466702514283</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="10">
@@ -703,13 +703,13 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1.869165183669233</v>
+        <v>1.792085984191247</v>
       </c>
       <c r="E12" t="n">
-        <v>2.440247180488127</v>
+        <v>2.30562367329171</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.400000000000001</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="13">
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.687500003102605</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>1.667871186632594</v>
+        <v>1.679523327549644</v>
       </c>
       <c r="E13" t="n">
-        <v>2.308261293156538</v>
+        <v>2.255890103140664</v>
       </c>
       <c r="F13" t="n">
-        <v>3.833048477399585</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.650000350472351</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2.15206879893975</v>
+        <v>2.065265154644854</v>
       </c>
       <c r="E14" t="n">
-        <v>2.29934337365715</v>
+        <v>2.236275180290957</v>
       </c>
       <c r="F14" t="n">
-        <v>-29.65376897181335</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="15">
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.588869205786832</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>1.525805111305946</v>
+        <v>1.579563606819246</v>
       </c>
       <c r="E15" t="n">
-        <v>2.314314734119745</v>
+        <v>2.246876261051797</v>
       </c>
       <c r="F15" t="n">
-        <v>17.54015947710564</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.329982285208149</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>1.505975226741767</v>
+        <v>1.519908975736043</v>
       </c>
       <c r="E16" t="n">
-        <v>2.323948929149438</v>
+        <v>2.243358883932038</v>
       </c>
       <c r="F16" t="n">
-        <v>20.08614352939507</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.544888126067967</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>1.62085822280016</v>
+        <v>1.609174033986064</v>
       </c>
       <c r="E17" t="n">
-        <v>2.251255690509302</v>
+        <v>2.252658153515954</v>
       </c>
       <c r="F17" t="n">
-        <v>9.331014979638248</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10.74999958569012</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>1.965053746244561</v>
+        <v>1.969086021505376</v>
       </c>
       <c r="E21" t="n">
-        <v>2.225223972881731</v>
+        <v>2.226010066256551</v>
       </c>
       <c r="F21" t="n">
-        <v>-14.74999931840538</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="22">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.49999724594986</v>
+        <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>1.837365542513276</v>
+        <v>1.829301075268817</v>
       </c>
       <c r="E22" t="n">
-        <v>1.877117904279348</v>
+        <v>1.874330498731272</v>
       </c>
       <c r="F22" t="n">
-        <v>-45.49999717568916</v>
+        <v>-45</v>
       </c>
     </row>
     <row r="23">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.984000000000001</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>1.498505376344086</v>
+        <v>1.471774193548387</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1438664855155</v>
+        <v>2.113486927441152</v>
       </c>
       <c r="F23" t="n">
-        <v>22.936</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
@@ -988,16 +988,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.285600000000001</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>1.479837634408602</v>
+        <v>1.497311827956989</v>
       </c>
       <c r="E24" t="n">
-        <v>2.157944243370415</v>
+        <v>2.183060500940319</v>
       </c>
       <c r="F24" t="n">
-        <v>24.8424</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6.984000000000001</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>1.498505376344086</v>
+        <v>1.471774193548387</v>
       </c>
       <c r="E25" t="n">
-        <v>2.1438664855155</v>
+        <v>2.113486927441152</v>
       </c>
       <c r="F25" t="n">
-        <v>22.936</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
